--- a/results_evaluations.xlsx
+++ b/results_evaluations.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t xml:space="preserve">Prompt 1 results</t>
   </si>
@@ -51,6 +51,9 @@
     <t xml:space="preserve">Risultato errato senza allucinazioni</t>
   </si>
   <si>
+    <t xml:space="preserve">Ragionamento corretto</t>
+  </si>
+  <si>
     <t>+</t>
   </si>
   <si>
@@ -84,7 +87,7 @@
     <t xml:space="preserve">ha inventato l'incremento di elevazione</t>
   </si>
   <si>
-    <t xml:space="preserve">Non ha capito che la cichiesta dell'utente non era riguardante il servizio offerto</t>
+    <t xml:space="preserve">Non ha capito che la richiesta dell'utente non era riguardante il servizio offerto</t>
   </si>
   <si>
     <t xml:space="preserve">ha inventato i chilometri giornalieri</t>
@@ -103,7 +106,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -113,6 +116,18 @@
     <font>
       <sz val="11.000000"/>
       <color theme="1" tint="0"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color indexed="2"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color theme="7" tint="0"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -137,7 +152,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="16">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -214,6 +229,37 @@
       <left style="thin">
         <color theme="1"/>
       </left>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
       <right style="thin">
         <color theme="1"/>
       </right>
@@ -225,6 +271,42 @@
       <left style="thin">
         <color theme="1"/>
       </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin">
         <color theme="1"/>
       </right>
@@ -238,41 +320,6 @@
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="none"/>
       <right style="thin">
         <color theme="1"/>
       </right>
@@ -286,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="41">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -300,65 +347,102 @@
     <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="1" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-      <protection hidden="0" locked="1"/>
+    <xf fontId="2" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -861,10 +945,11 @@
   <cols>
     <col bestFit="1" min="4" max="4" width="99.28125"/>
     <col bestFit="1" min="14" max="14" width="10.7109375"/>
-    <col bestFit="1" min="18" max="18" width="14.140625"/>
-    <col bestFit="1" min="19" max="19" width="28.57421875"/>
-    <col bestFit="1" min="20" max="20" width="30.140625"/>
-    <col bestFit="1" min="22" max="22" width="10.7109375"/>
+    <col bestFit="1" min="17" max="17" width="14.140625"/>
+    <col bestFit="1" min="18" max="18" width="28.57421875"/>
+    <col bestFit="1" min="19" max="19" width="30.140625"/>
+    <col bestFit="1" min="20" max="20" width="20.7109375"/>
+    <col bestFit="1" min="21" max="21" width="10.7109375"/>
   </cols>
   <sheetData>
     <row r="2" ht="14.25">
@@ -894,615 +979,634 @@
       <c r="N2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="R2" t="s">
+      <c r="Q2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="S2" t="s">
+      <c r="R2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="T2" t="s">
+      <c r="S2" s="7" t="s">
         <v>10</v>
       </c>
+      <c r="T2" s="8" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="B3">
+      <c r="B3" s="9">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="5">
+      <c r="D3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="12">
         <v>1</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="R3" s="8">
+      <c r="H3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="Q3" s="14">
         <f>18/25</f>
         <v>0.71999999999999997</v>
       </c>
-      <c r="S3" s="8">
+      <c r="R3" s="15">
         <f>7/25</f>
         <v>0.28000000000000003</v>
       </c>
+      <c r="S3" s="16"/>
+      <c r="T3" s="6"/>
     </row>
     <row r="4" ht="14.25">
-      <c r="B4">
+      <c r="B4" s="17">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="9">
+      <c r="C4" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="G4" s="20">
         <v>2</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="13"/>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="B5" s="17">
+        <v>3</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="19"/>
+      <c r="G5" s="20">
+        <v>3</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="B6" s="17">
+        <v>4</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="19"/>
+      <c r="G6" s="20">
+        <v>4</v>
+      </c>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="B7" s="17">
+        <v>5</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="19"/>
+      <c r="G7" s="20">
+        <v>5</v>
+      </c>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="B8" s="17">
+        <v>6</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="21">
+        <v>6</v>
+      </c>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="B9" s="17">
+        <v>7</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="19"/>
+      <c r="G9" s="20">
+        <v>7</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N9" s="13"/>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="B10" s="17">
+        <v>8</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="22">
+        <v>8</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="B11" s="17">
+        <v>9</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="19"/>
+      <c r="G11" s="20">
+        <v>9</v>
+      </c>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N11" s="13"/>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="B12" s="17">
+        <v>10</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="22">
+        <v>10</v>
+      </c>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="13"/>
+      <c r="L12" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="B13" s="17">
+        <v>11</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="22">
+        <v>11</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="B14" s="17">
+        <v>12</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="19"/>
+      <c r="G14" s="21">
+        <v>12</v>
+      </c>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="B15" s="17">
         <v>13</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="6" t="s">
+      <c r="C15" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="22">
         <v>13</v>
       </c>
-      <c r="M4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" s="7"/>
-    </row>
-    <row r="5" ht="14.25">
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="9">
-        <v>3</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-    </row>
-    <row r="6" ht="14.25">
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="9">
-        <v>4</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-    </row>
-    <row r="7" ht="14.25">
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="9">
-        <v>5</v>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-    </row>
-    <row r="8" ht="14.25">
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="H15" s="13"/>
+      <c r="I15" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" s="13"/>
+      <c r="K15" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="B16" s="17">
+        <v>14</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="22">
+        <v>14</v>
+      </c>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="N16" s="13"/>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="B17" s="17">
         <v>15</v>
       </c>
-      <c r="D8" t="s">
+      <c r="C17" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="19"/>
+      <c r="G17" s="21">
+        <v>15</v>
+      </c>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="B18" s="17">
         <v>16</v>
       </c>
-      <c r="G8" s="10">
-        <v>6</v>
-      </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-    </row>
-    <row r="9" ht="14.25">
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="9">
-        <v>7</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="N9" s="7"/>
-    </row>
-    <row r="10" ht="14.25">
-      <c r="B10">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C18" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="21">
+        <v>16</v>
+      </c>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="B19" s="17">
         <v>17</v>
       </c>
-      <c r="G10" s="11">
-        <v>8</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-    </row>
-    <row r="11" ht="14.25">
-      <c r="B11">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="9">
-        <v>9</v>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="N11" s="7"/>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="B12">
-        <v>10</v>
-      </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C19" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="19"/>
+      <c r="G19" s="21">
+        <v>17</v>
+      </c>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="B20" s="17">
         <v>18</v>
       </c>
-      <c r="G12" s="11">
-        <v>10</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="B13">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C20" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="19"/>
+      <c r="G20" s="21">
+        <v>18</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N20" s="13"/>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="B21" s="17">
         <v>19</v>
       </c>
-      <c r="G13" s="11">
-        <v>11</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="B14">
+      <c r="C21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="19"/>
+      <c r="G21" s="21">
+        <v>19</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="B22" s="17">
+        <v>20</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="19"/>
+      <c r="G22" s="21">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="B23" s="17">
+        <v>21</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="19"/>
+      <c r="G23" s="21">
+        <v>21</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N23" s="13"/>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="B24" s="17">
+        <v>22</v>
+      </c>
+      <c r="C24" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="10">
+      <c r="D24" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="22">
+        <v>22</v>
+      </c>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="B25" s="17">
+        <v>23</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="19"/>
+      <c r="G25" s="21">
+        <v>23</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="B26" s="17">
+        <v>24</v>
+      </c>
+      <c r="C26" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-    </row>
-    <row r="15" ht="14.25">
-      <c r="B15">
-        <v>13</v>
-      </c>
-      <c r="C15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="11">
-        <v>13</v>
-      </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" s="7"/>
-      <c r="K15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="B16">
-        <v>14</v>
-      </c>
-      <c r="C16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" s="11">
-        <v>14</v>
-      </c>
-      <c r="H16" s="7"/>
-      <c r="I16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="N16" s="7"/>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="B17">
+      <c r="D26" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="22">
+        <v>24</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N26" s="13"/>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="B27" s="25">
+        <v>25</v>
+      </c>
+      <c r="C27" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="10">
-        <v>15</v>
-      </c>
-      <c r="H17" s="7"/>
-      <c r="I17" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-    </row>
-    <row r="18" ht="14.25">
-      <c r="B18">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="10">
-        <v>16</v>
-      </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="7"/>
-    </row>
-    <row r="19" ht="14.25">
-      <c r="B19">
-        <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="10">
-        <v>17</v>
-      </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-    </row>
-    <row r="20" ht="14.25">
-      <c r="B20">
-        <v>18</v>
-      </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="10">
-        <v>18</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="N20" s="7"/>
-    </row>
-    <row r="21" ht="14.25">
-      <c r="B21">
-        <v>19</v>
-      </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="10">
-        <v>19</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="7"/>
-    </row>
-    <row r="22" ht="14.25">
-      <c r="B22">
-        <v>20</v>
-      </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="10">
-        <v>20</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-    </row>
-    <row r="23" ht="14.25">
-      <c r="B23">
-        <v>21</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="10">
-        <v>21</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="N23" s="7"/>
-    </row>
-    <row r="24" ht="14.25">
-      <c r="B24">
-        <v>22</v>
-      </c>
-      <c r="C24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="11">
-        <v>22</v>
-      </c>
-      <c r="H24" s="7"/>
-      <c r="I24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-    </row>
-    <row r="25" ht="14.25">
-      <c r="B25">
-        <v>23</v>
-      </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="10">
-        <v>23</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-    </row>
-    <row r="26" ht="14.25">
-      <c r="B26">
-        <v>24</v>
-      </c>
-      <c r="C26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" s="11">
-        <v>24</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="N26" s="7"/>
-    </row>
-    <row r="27" ht="14.25">
-      <c r="B27">
+      <c r="D27" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="28">
         <v>25</v>
       </c>
-      <c r="C27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" s="12">
-        <v>25</v>
-      </c>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
     </row>
     <row r="28" ht="14.25"/>
     <row r="31" ht="14.25">
-      <c r="B31" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="16"/>
-      <c r="G31" s="17"/>
+      <c r="B31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="3"/>
+      <c r="G31" s="30"/>
       <c r="H31" s="4" t="s">
         <v>1</v>
       </c>
@@ -1524,381 +1628,555 @@
       <c r="N31" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="Q31" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="R31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="S31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="T31" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="32" ht="14.25">
-      <c r="B32" s="18">
+      <c r="B32" s="31">
         <v>1</v>
       </c>
-      <c r="G32" s="19">
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
+      <c r="G32" s="12">
         <v>1</v>
       </c>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
+      <c r="H32" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" s="34"/>
+      <c r="L32" s="34"/>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
+      <c r="Q32" s="15">
+        <f>20/25</f>
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="R32" s="15">
+        <f>5/25</f>
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="B33" s="18">
+      <c r="B33" s="35">
         <v>2</v>
       </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="19"/>
       <c r="G33" s="21">
         <v>2</v>
       </c>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
+      <c r="H33" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="M33" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="N33" s="13"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="B34" s="18">
+      <c r="B34" s="35">
         <v>3</v>
       </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="19"/>
       <c r="G34" s="21">
         <v>3</v>
       </c>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
+      <c r="H34" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
     </row>
     <row r="35" ht="14.25">
-      <c r="B35" s="18">
+      <c r="B35" s="35">
         <v>4</v>
       </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="19"/>
       <c r="G35" s="21">
         <v>4</v>
       </c>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="B36" s="18">
+      <c r="B36" s="35">
         <v>5</v>
       </c>
-      <c r="G36" s="21">
+      <c r="C36" s="18"/>
+      <c r="D36" s="19"/>
+      <c r="G36" s="22">
         <v>5</v>
       </c>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
     </row>
     <row r="37" ht="14.25">
-      <c r="B37" s="18">
+      <c r="B37" s="35">
         <v>6</v>
       </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="19"/>
       <c r="G37" s="21">
         <v>6</v>
       </c>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
     </row>
     <row r="38" ht="14.25">
-      <c r="B38" s="18">
+      <c r="B38" s="35">
         <v>7</v>
       </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="19"/>
       <c r="G38" s="21">
         <v>7</v>
       </c>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
+      <c r="H38" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="M38" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="N38" s="13"/>
     </row>
     <row r="39" ht="14.25">
-      <c r="B39" s="18">
+      <c r="B39" s="35">
         <v>8</v>
       </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="19"/>
       <c r="G39" s="21">
         <v>8</v>
       </c>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
     </row>
     <row r="40" ht="14.25">
-      <c r="B40" s="18">
+      <c r="B40" s="35">
         <v>9</v>
       </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="19"/>
       <c r="G40" s="21">
         <v>9</v>
       </c>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="M40" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="N40" s="13"/>
     </row>
     <row r="41" ht="14.25">
-      <c r="B41" s="18">
+      <c r="B41" s="35">
         <v>10</v>
       </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="19"/>
       <c r="G41" s="21">
         <v>10</v>
       </c>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-      <c r="N41" s="7"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
     </row>
     <row r="42" ht="14.25">
-      <c r="B42" s="18">
+      <c r="B42" s="35">
         <v>11</v>
       </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="19"/>
       <c r="G42" s="21">
         <v>11</v>
       </c>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+      <c r="M42" s="13"/>
+      <c r="N42" s="13"/>
     </row>
     <row r="43" ht="14.25">
-      <c r="B43" s="18">
+      <c r="B43" s="35">
         <v>12</v>
       </c>
-      <c r="G43" s="21">
+      <c r="C43" s="18"/>
+      <c r="D43" s="19"/>
+      <c r="G43" s="22">
         <v>12</v>
       </c>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="7"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="K43" s="13"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
     </row>
     <row r="44" ht="14.25">
-      <c r="B44" s="18">
+      <c r="B44" s="35">
         <v>13</v>
       </c>
+      <c r="C44" s="18"/>
+      <c r="D44" s="19"/>
       <c r="G44" s="21">
         <v>13</v>
       </c>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-      <c r="N44" s="7"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="B45" s="18">
-        <v>14</v>
-      </c>
+      <c r="B45" s="35">
+        <v>14</v>
+      </c>
+      <c r="C45" s="18"/>
+      <c r="D45" s="19"/>
       <c r="G45" s="21">
         <v>14</v>
       </c>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="7"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="13"/>
+      <c r="M45" s="13"/>
+      <c r="N45" s="13"/>
     </row>
     <row r="46" ht="14.25">
-      <c r="B46" s="18">
+      <c r="B46" s="35">
         <v>15</v>
       </c>
+      <c r="C46" s="18"/>
+      <c r="D46" s="19"/>
       <c r="G46" s="21">
         <v>15</v>
       </c>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
     </row>
     <row r="47" ht="14.25">
-      <c r="B47" s="18">
+      <c r="B47" s="35">
         <v>16</v>
       </c>
-      <c r="G47" s="21">
+      <c r="C47" s="18"/>
+      <c r="D47" s="19"/>
+      <c r="G47" s="22">
         <v>16</v>
       </c>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="7"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13"/>
     </row>
     <row r="48" ht="14.25">
-      <c r="B48" s="18">
+      <c r="B48" s="35">
         <v>17</v>
       </c>
+      <c r="C48" s="18"/>
+      <c r="D48" s="19"/>
       <c r="G48" s="21">
         <v>17</v>
       </c>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="13"/>
+      <c r="M48" s="13"/>
+      <c r="N48" s="13"/>
     </row>
     <row r="49" ht="14.25">
-      <c r="B49" s="18">
+      <c r="B49" s="35">
         <v>18</v>
       </c>
+      <c r="C49" s="18"/>
+      <c r="D49" s="19"/>
       <c r="G49" s="21">
         <v>18</v>
       </c>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
+      <c r="H49" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="M49" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="N49" s="13"/>
     </row>
     <row r="50" ht="14.25">
-      <c r="B50" s="18">
+      <c r="B50" s="35">
         <v>19</v>
       </c>
+      <c r="C50" s="18"/>
+      <c r="D50" s="19"/>
       <c r="G50" s="21">
         <v>19</v>
       </c>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-      <c r="N50" s="7"/>
+      <c r="H50" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
     </row>
     <row r="51" ht="14.25">
-      <c r="B51" s="18">
+      <c r="B51" s="35">
         <v>20</v>
       </c>
+      <c r="C51" s="18"/>
+      <c r="D51" s="19"/>
       <c r="G51" s="21">
         <v>20</v>
       </c>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="7"/>
+      <c r="H51" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
     </row>
     <row r="52" ht="14.25">
-      <c r="B52" s="18">
+      <c r="B52" s="35">
         <v>21</v>
       </c>
+      <c r="C52" s="18"/>
+      <c r="D52" s="19"/>
       <c r="G52" s="21">
         <v>21</v>
       </c>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
+      <c r="H52" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="M52" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="N52" s="13"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="B53" s="18">
+      <c r="B53" s="35">
         <v>22</v>
       </c>
+      <c r="C53" s="18"/>
+      <c r="D53" s="19"/>
       <c r="G53" s="21">
         <v>22</v>
       </c>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="7"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="B54" s="18">
+      <c r="B54" s="35">
         <v>23</v>
       </c>
+      <c r="C54" s="18"/>
+      <c r="D54" s="19"/>
       <c r="G54" s="21">
         <v>23</v>
       </c>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="7"/>
+      <c r="H54" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13"/>
     </row>
     <row r="55" ht="14.25">
-      <c r="B55" s="18">
+      <c r="B55" s="35">
         <v>24</v>
       </c>
-      <c r="G55" s="21">
+      <c r="C55" s="18"/>
+      <c r="D55" s="19"/>
+      <c r="G55" s="22">
         <v>24</v>
       </c>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="7"/>
+      <c r="H55" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="M55" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="N55" s="13"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="B56" s="18">
+      <c r="B56" s="37">
         <v>25</v>
       </c>
-      <c r="G56" s="22">
+      <c r="C56" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="27"/>
+      <c r="G56" s="39">
         <v>25</v>
       </c>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-      <c r="K56" s="13"/>
-      <c r="L56" s="13"/>
-      <c r="M56" s="13"/>
-      <c r="N56" s="13"/>
+      <c r="H56" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
+      <c r="L56" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="M56" s="29"/>
+      <c r="N56" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="2">
